--- a/web/public/plantilla-productos-vecired.xlsx
+++ b/web/public/plantilla-productos-vecired.xlsx
@@ -138,7 +138,7 @@
     <t>3.</t>
   </si>
   <si>
-    <t>Guardá el archivo y subilo desde tu panel de Vecired, en Productos &gt; Cargar o actualizar desde Excel.</t>
+    <t>Guardá el archivo y subilo desde tu panel de VeciRed, en Productos &gt; Cargar o actualizar desde Excel.</t>
   </si>
   <si>
     <t>4.</t>
